--- a/artfynd/A 46341-2025 artfynd.xlsx
+++ b/artfynd/A 46341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84332732</v>
+        <v>123329478</v>
       </c>
       <c r="B2" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +704,27 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Arkelstorpsvägen, Knutstorp, 500 m NNV., Sk</t>
+          <t>Knutstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454066.9135770989</v>
+        <v>454067</v>
       </c>
       <c r="R2" t="n">
-        <v>6221513.35525359</v>
+        <v>6221486</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +768,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Joakim Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Joakim Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84332733</v>
+        <v>77454960</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +791,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arkelstorpsvägen, Knutstorp, 500 m NNV., Sk</t>
+          <t>Arkelstorpsvägen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454066.9135770989</v>
+        <v>454065</v>
       </c>
       <c r="R3" t="n">
-        <v>6221513.35525359</v>
+        <v>6221511</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,36 +878,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Stefan Cherrug</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Stefan Cherrug</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84332736</v>
+        <v>123329469</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,37 +905,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Arkelstorpsvägen, Knutstorp, 500 m NNV., Sk</t>
+          <t>Knutstorp, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454066.9135770989</v>
+        <v>454067</v>
       </c>
       <c r="R4" t="n">
-        <v>6221513.35525359</v>
+        <v>6221486</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,58 +983,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Joakim Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Joakim Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>84332737</v>
+        <v>84332732</v>
       </c>
       <c r="B5" t="n">
-        <v>101859</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220464</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lundbräsma</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cardamine impatiens</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454066.9135770989</v>
+        <v>454067</v>
       </c>
       <c r="R5" t="n">
-        <v>6221513.35525359</v>
+        <v>6221513</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,21 +1067,11 @@
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1117,11 +1080,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1138,15 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96744217</v>
+        <v>84332737</v>
       </c>
       <c r="B6" t="n">
-        <v>101859</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,14 +1127,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knutstorp, 370 m NNV, västra sidan av vägen., Sk</t>
+          <t>Arkelstorpsvägen, Knutstorp, 500 m NNV., Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454057.8201557727</v>
+        <v>454067</v>
       </c>
       <c r="R6" t="n">
-        <v>6221498.409205019</v>
+        <v>6221513</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,27 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>LBF exkursion</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1180,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1253,22 +1191,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson, Ulf Ryde, Staffan Nilsson, Torbjörn Tyler</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123329469</v>
+        <v>96744217</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104808</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,45 +1209,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lundbräsma</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cardamine impatiens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knutstorp, Sk</t>
+          <t>Knutstorp, 370 m NNV, västra sidan av vägen., Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454067</v>
+        <v>454058</v>
       </c>
       <c r="R7" t="n">
-        <v>6221486</v>
+        <v>6221498</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,12 +1263,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2021-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2021-10-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>LBF exkursion</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,77 +1284,69 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joakim Hagström</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joakim Hagström</t>
+          <t>Charlotte Wigermo, Åke Svensson, Ulf Ryde, Staffan Nilsson, Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123329478</v>
+        <v>84332736</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knutstorp, Sk</t>
+          <t>Arkelstorpsvägen, Knutstorp, 500 m NNV., Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>454067</v>
       </c>
       <c r="R8" t="n">
-        <v>6221486</v>
+        <v>6221513</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,12 +1370,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,19 +1386,126 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Hagström</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Hagström</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>84332733</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Arkelstorpsvägen, Knutstorp, 500 m NNV., Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>454067</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6221513</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-04-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-04-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46341-2025 artfynd.xlsx
+++ b/artfynd/A 46341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123329478</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77454960</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123329469</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84332732</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84332737</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96744217</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84332736</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,8 +1546,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84332733</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>